--- a/xls/ability - 複製.xlsx
+++ b/xls/ability - 複製.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="46">
   <si>
     <t>strong</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -205,6 +205,10 @@
   <si>
     <t>{"stage":"cast","scope":"self","type":"hot","a":5,"dur":5,"icon":"❤️","id":"heal"},
 {"stage":"cast","scope":"self","type":"buff","key":"str","a":1,"dur":100,"stack":1,"icon":"💪","id":"strong"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>spell</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -644,7 +648,7 @@
         <v>20</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>41</v>
@@ -696,7 +700,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="46.8">
+    <row r="6" spans="1:9" ht="31.2">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
